--- a/sample_excel_files/students_bulk_upload.xlsx
+++ b/sample_excel_files/students_bulk_upload.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +28,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -40,8 +39,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
-        <bgColor rgb="000F172A"/>
+        <fgColor rgb="00366092"/>
+        <bgColor rgb="00366092"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,10 +56,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -430,18 +430,18 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Reg No</t>
+          <t>RegNo</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -466,308 +466,308 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Current Year</t>
+          <t>Year</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>S2024001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>12101001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Rahul Sharma</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>rahul.sharma@pict.edu</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>9876543210</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2002-03-15</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2003-03-15</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>12101002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Priya Singh</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>priya.singh@pict.edu</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>9876543211</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2003-06-20</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>12101003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Arjun Patel</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>arjun.patel@pict.edu</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9876543212</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2003-01-10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>12101004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Neha Gupta</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>neha.gupta@pict.edu</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9876543213</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2004-05-25</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>S2024002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Priya Patel</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>priya.patel@pict.edu</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>9876543211</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2001-07-22</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>S2024003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Amit Kumar</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>amit.kumar@pict.edu</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>9876543212</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2003-01-10</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>12101005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Vikram Desai</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>vikram.desai@pict.edu</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9876543214</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2004-08-12</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>12101006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Anjali Nair</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>anjali.nair@pict.edu</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9876543215</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2004-02-18</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>12101007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Suresh Kumar</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>suresh.kumar@pict.edu</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9876543216</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2005-07-22</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>S2024004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sneha Desai</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>sneha.desai@pict.edu</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>9876543213</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2002-11-05</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>S2024005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rohan Joshi</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>rohan.joshi@pict.edu</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>9876543214</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2001-09-18</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>S2024006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Anjali Mehta</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>anjali.mehta@pict.edu</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>9876543215</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2003-05-28</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>12101008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Divya Sharma</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>divya.sharma@pict.edu</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9876543217</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2005-11-30</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>S2024007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Vikram Singh</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>vikram.singh@pict.edu</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>9876543216</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2002-12-14</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>S2024008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Pooja Reddy</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>pooja.reddy@pict.edu</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>9876543217</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2001-04-09</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>S2024009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Karan Verma</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>karan.verma@pict.edu</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>12101009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Rohan Singh</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>rohan.singh@pict.edu</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>9876543218</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2003-08-21</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2005-04-14</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>S2024010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Divya Nair</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>divya.nair@pict.edu</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>12101010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Zara Khan</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>zara.khan@pict.edu</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>9876543219</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2002-06-30</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2005-09-08</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/sample_excel_files/students_bulk_upload.xlsx
+++ b/sample_excel_files/students_bulk_upload.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,17 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="000c4a6e"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000c4a6e"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,8 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00366092"/>
-        <bgColor rgb="00366092"/>
+        <fgColor rgb="000e7490"/>
+        <bgColor rgb="000e7490"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00dbeafe"/>
+        <bgColor rgb="00dbeafe"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,12 +71,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,21 +444,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RegNo</t>
+          <t>RegNo/PRN</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -467,310 +485,287 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Department</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>IMPORTANT: Use your institution's PRN/Reg No. Each student has a unique permanent registration number. Department is optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>12101001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Rahul Sharma</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>rahul.sharma@pict.edu</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>9876543210</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>2003-03-15</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Computer Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>12101002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Priya Singh</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>priya.singh@pict.edu</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>9876543211</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>2003-06-20</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>12101003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Arjun Patel</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>arjun.patel@pict.edu</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>9876543212</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>2003-01-10</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Electronics Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>12101004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Neha Gupta</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>neha.gupta@pict.edu</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>9876543213</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2004-05-25</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>12101005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Vikram Desai</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>vikram.desai@pict.edu</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>9876543214</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>2004-08-12</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>12101006</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Anjali Nair</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>anjali.nair@pict.edu</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9876543215</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2004-02-18</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>12101007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Suresh Kumar</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>suresh.kumar@pict.edu</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9876543216</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2005-07-22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>12101008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Divya Sharma</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>divya.sharma@pict.edu</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9876543217</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2005-11-30</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>FORMAT GUIDE:</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>12101009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Rohan Singh</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>rohan.singh@pict.edu</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9876543218</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2005-04-14</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1</v>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>• RegNo/PRN: Unique permanent registration number from your institution</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>12101010</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Zara Khan</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>zara.khan@pict.edu</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9876543219</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2005-09-08</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>• Name: Student name (Text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>• Email: Student email address (must be valid email format)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>• Mobile: 10-digit mobile number without spaces or dashes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>• DOB: Date of birth in YYYY-MM-DD format (e.g., 2003-03-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>• Year: Current year of study (1, 2, 3, or 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>IMPORTANT NOTES:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>✓ Each student's PRN/RegNo must be UNIQUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>✓ System uses your institution's registration numbers (NOT auto-generated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>✓ Duplicate RegNo, email, or mobile numbers will be rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>✓ All fields are REQUIRED</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>